--- a/outputs/3_1_indicadores.xlsx
+++ b/outputs/3_1_indicadores.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Otras actividades de servicios comunitarios, sociales y personales</t>
   </si>
   <si>
-    <t xml:space="preserve">Otras actividades / No informa</t>
+    <t xml:space="preserve">Actividades no clasificadas / Sin información</t>
   </si>
   <si>
     <t xml:space="preserve">Registro Único Tributario - RUT (P1633)</t>
